--- a/artfynd/A 64533-2023 artfynd.xlsx
+++ b/artfynd/A 64533-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64533-2023 artfynd.xlsx
+++ b/artfynd/A 64533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75659837</v>
+        <v>81614052</v>
       </c>
       <c r="B2" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>101675</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624618.2195942969</v>
+        <v>624672</v>
       </c>
       <c r="R2" t="n">
-        <v>6703533.541697689</v>
+        <v>6703530</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2009-05-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-05-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gamla kläckhål i fnöskticka på björkhögstubbe, omkr. 72 cm, i en 15-20 årig granplantering.</t>
+          <t>Gamla kläckhål i veden på asplåga, omkr. 105 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,19 +767,14 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granplantering med kvarlämnade, äldre lövträd.</t>
-        </is>
-      </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,44 +792,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75811629</v>
+        <v>75659836</v>
       </c>
       <c r="B3" t="n">
-        <v>4964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101608</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
@@ -861,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624676.49681315</v>
+        <v>624598</v>
       </c>
       <c r="R3" t="n">
-        <v>6703493.077437358</v>
+        <v>6703548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,24 +865,14 @@
           <t>2009-05-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-05-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 kläckhål i barken på levande asp, omkr. 160 cm, i en 15-20 årig granplantering.</t>
+          <t>Gamla kläckhål i fnöskticka på björkhögstubbe, omkr. 77 cm, i en 15-20 årig granplantering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +891,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81614052</v>
+        <v>75659837</v>
       </c>
       <c r="B4" t="n">
-        <v>4808</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -998,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624672.2588759264</v>
+        <v>624618</v>
       </c>
       <c r="R4" t="n">
-        <v>6703529.969445365</v>
+        <v>6703534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,24 +987,14 @@
           <t>2009-05-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-05-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gamla kläckhål i veden på asplåga, omkr. 105 cm.</t>
+          <t>Gamla kläckhål i fnöskticka på björkhögstubbe, omkr. 72 cm, i en 15-20 årig granplantering.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,14 +1006,19 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granplantering med kvarlämnade, äldre lövträd.</t>
+        </is>
+      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,6 +1033,128 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75659838</v>
+      </c>
+      <c r="B5" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stortyllen, N om Rämsön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>624703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6703487</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-05-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla kläckhål i fnöskticka på björkhögstubbe, omkr. 105 cm, i en 15-20 årig granplantering.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granplantering med kvarlämnade, äldre lövträd.</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64533-2023 artfynd.xlsx
+++ b/artfynd/A 64533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81614052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75659836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75659837</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1155,8 +1175,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75659838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>